--- a/ExcelTool/Excel/Excels/StartConfig/Client/WorldLineConfig.xlsx
+++ b/ExcelTool/Excel/Excels/StartConfig/Client/WorldLineConfig.xlsx
@@ -541,7 +541,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
